--- a/data-vh/Неделя_23.02-01.03_2026_ВХ.xlsx
+++ b/data-vh/Неделя_23.02-01.03_2026_ВХ.xlsx
@@ -2,39 +2,55 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист_1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист_1'!$A$1:$Q$7</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4ECC5"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -42,15 +58,149 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -125,9 +275,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -165,7 +315,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -199,6 +349,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,9 +384,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -410,468 +562,525 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.42578125" defaultRowHeight="11.4" customHeight="1"/>
+  <cols>
+    <col width="5.140625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="5.28515625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="3.7109375" customWidth="1" style="1" min="3" max="3"/>
+    <col width="5" customWidth="1" style="1" min="4" max="4"/>
+    <col width="10.140625" customWidth="1" style="1" min="5" max="5"/>
+    <col width="22.5703125" customWidth="1" style="1" min="6" max="6"/>
+    <col width="21" customWidth="1" style="1" min="7" max="7"/>
+    <col width="29.7109375" customWidth="1" style="1" min="8" max="8"/>
+    <col width="18.5703125" customWidth="1" style="1" min="9" max="9"/>
+    <col width="32.140625" customWidth="1" style="1" min="10" max="10"/>
+    <col width="13.7109375" customWidth="1" style="1" min="11" max="11"/>
+    <col width="7.28515625" customWidth="1" style="1" min="12" max="12"/>
+    <col width="8.28515625" customWidth="1" style="1" min="13" max="13"/>
+    <col width="27.5703125" customWidth="1" style="1" min="14" max="14"/>
+    <col width="30.7109375" customWidth="1" style="1" min="15" max="15"/>
+    <col width="74.7109375" customWidth="1" style="1" min="16" max="16"/>
+    <col width="44.28515625" customWidth="1" style="1" min="17" max="17"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="25.95" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>Поставщик/Переработчик</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Место проведения контроля</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Номенклатура</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>Группа номенклатуры</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="15" t="inlineStr">
         <is>
           <t>Кол., шт.</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="15" t="inlineStr">
         <is>
           <t>Кол., кг</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="15" t="inlineStr">
         <is>
           <t>Вид несоответствия</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>Критичность несоответствия</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="15" t="inlineStr">
         <is>
           <t>Несоответствие</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="15" t="inlineStr">
         <is>
           <t>Решение</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="10.95" customHeight="1">
+      <c r="A2" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>В00-0000037</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" s="21" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>24.02.2026</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР18 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="10" t="n">
         <v>1171.38</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Брызги металла, отс. замыкание таврового шва («закольцовки»).</t>
         </is>
       </c>
+      <c r="Q2" s="7" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" ht="10.95" customHeight="1">
+      <c r="A3" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>В00-0000037</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>24.02.2026</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР14 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="10" t="n">
         <v>1318.94</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
+      <c r="Q3" s="7" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" ht="10.95" customHeight="1">
+      <c r="A4" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>В00-0000037</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>24.02.2026</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР17 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="10" t="n">
         <v>1853.49</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
+      <c r="Q4" s="7" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" ht="10.95" customHeight="1">
+      <c r="A5" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>В00-0000037</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>24.02.2026</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР6 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="9" t="n">
         <v>809.21</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
+      <c r="Q5" s="7" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" ht="22.95" customHeight="1">
+      <c r="A6" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>В00-0000038</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>25.02.2026</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-000871 от 18.02.2026 0:00:00</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>ИО ТЕХНОЛОДЖИ ООО (ЭДО Такском)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>_уу_Блок световой ИСС 2-200 24В/8Вт IP68</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>ОМФП</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>Кабельный ввод не закреплен на задней панели</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" s="7" t="inlineStr">
         <is>
           <t>Замена поставщиком</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" ht="22.95" customHeight="1">
+      <c r="A7" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>В00-0000039</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>26.02.2026</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>КЕДР-1 ООО (ЭДО ЗП с 21.01.2026)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>КЕДР-1 ООО (ЭДО ЗП с 21.01.2026)</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил Р 44,4х22,2/30х2 1 А 996х1000 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>Настилы прессованные</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="10" t="n">
         <v>3656.25</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>1. Брызги металла диаметром более 1,5 мм. 2. Остатки сварочной проволоки. 3. Натёки.</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранить силами переработчика</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:Q7">
+    <filterColumn colId="1" hiddenButton="0" showButton="0"/>
+    <filterColumn colId="2" hiddenButton="0" showButton="0"/>
+  </autoFilter>
+  <mergeCells count="7">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0" footer="0"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" pageOrder="overThenDown"/>
 </worksheet>
 </file>